--- a/docs/slide_data.xlsx
+++ b/docs/slide_data.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_EB45A67B026F236B240BE4472FA54CAF4993320B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B819D05B-D5E2-498C-8407-8D23D2BD9738}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_EB45A67B026F236B240BE4472FA54CAF4993320B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20D3E7F4-B569-4395-87B3-3D33D660B538}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Name</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>Bob Jr</t>
+  </si>
+  <si>
+    <t>No news</t>
   </si>
 </sst>
 </file>
@@ -481,6 +484,9 @@
       <c r="F2" t="s">
         <v>8</v>
       </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
